--- a/sample_data/projectX_Timesheet_April 2024.xlsx
+++ b/sample_data/projectX_Timesheet_April 2024.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAB0263-CD6C-FF45-8884-6B5B6E565A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{D17B7CAD-D25E-4F20-8096-0A9ACC033B04}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20280" activeTab="1" xr2:uid="{D17B7CAD-D25E-4F20-8096-0A9ACC033B04}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="6" r:id="rId1"/>
@@ -721,6 +721,19 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -735,19 +748,6 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,6 +755,62 @@
   </cellStyles>
   <dxfs count="91">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1" tint="0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0066"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -772,6 +828,20 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -801,819 +871,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="0"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0066"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0066"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1651,11 +908,49 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1686,7 +981,45 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1711,6 +1044,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1747,6 +1099,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1766,6 +1137,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1785,6 +1175,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1804,6 +1213,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1823,7 +1251,45 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1848,6 +1314,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1884,6 +1369,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1903,6 +1407,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1922,6 +1445,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1941,6 +1483,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1960,7 +1521,45 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1985,6 +1584,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2021,6 +1639,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2040,6 +1677,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2059,6 +1715,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2078,6 +1753,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2097,10 +1791,48 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2116,6 +1848,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2146,6 +1897,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2165,6 +1935,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2184,6 +1973,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2203,6 +2011,25 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2222,10 +2049,48 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2238,6 +2103,31 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2262,6 +2152,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2277,6 +2185,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2292,6 +2218,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2307,17 +2251,54 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2334,6 +2315,25 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2400,62 +2400,62 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{86BD8C17-1601-4130-BC1E-DD75642252C4}" name="Table27" displayName="Table27" ref="E5:AS21" totalsRowCount="1" headerRowDxfId="90" dataDxfId="89">
   <tableColumns count="41">
-    <tableColumn id="40" xr3:uid="{0A54AE2F-C256-4AA4-81C3-E00ACCC76EC8}" name="Emp ID" dataDxfId="88" totalsRowDxfId="40"/>
-    <tableColumn id="39" xr3:uid="{9669CAB7-33E5-40E8-9ECD-BFA5F383C0BD}" name="Role as per SoW" dataDxfId="87" totalsRowDxfId="39">
+    <tableColumn id="40" xr3:uid="{0A54AE2F-C256-4AA4-81C3-E00ACCC76EC8}" name="Emp ID" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="39" xr3:uid="{9669CAB7-33E5-40E8-9ECD-BFA5F383C0BD}" name="Role as per SoW" dataDxfId="86" totalsRowDxfId="85">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table27[[#This Row],[Emp ID]],Table1[Emp ID],Table1[Role as per SoW])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{4449859A-55A6-45AA-8A96-FCC6309D5F60}" name="Name" totalsRowLabel="Total" dataDxfId="86" totalsRowDxfId="38">
+    <tableColumn id="1" xr3:uid="{4449859A-55A6-45AA-8A96-FCC6309D5F60}" name="Name" totalsRowLabel="Total" dataDxfId="84" totalsRowDxfId="83">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table27[[#This Row],[Emp ID]],Table1[Emp ID],Table1[Name])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{25895A40-683C-400E-B977-6736C26F70FF}" name="Max Billable Hours" totalsRowFunction="sum" dataDxfId="85" totalsRowDxfId="37">
+    <tableColumn id="2" xr3:uid="{25895A40-683C-400E-B977-6736C26F70FF}" name="Max Billable Hours" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81">
       <calculatedColumnFormula>IF(Table27[[#This Row],[Status]]="Active",SUM(COUNT(Table27[[#This Row],[1]:[31]]), COUNTIF(Table27[[#This Row],[1]:[31]],"OFF"))*_xlfn.XLOOKUP(Table27[[#This Row],[Name]],Table1[Name],Table1[Billable Hours per day]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{42257E96-50F7-4B29-B3B1-132233AB2AA6}" name="Actual Hours" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="36">
+    <tableColumn id="3" xr3:uid="{42257E96-50F7-4B29-B3B1-132233AB2AA6}" name="Actual Hours" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79">
       <calculatedColumnFormula>IF(Table27[[#This Row],[Status]]="Active",SUM(Table27[[#This Row],[1]:[31]]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C4F1F072-CB0B-4451-B5C6-05FB81DFFC03}" name="Rate" dataDxfId="83" totalsRowDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{6E3636B9-97B1-4231-848A-84020E8CD1A3}" name="Final Billing Amount" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="34">
+    <tableColumn id="4" xr3:uid="{C4F1F072-CB0B-4451-B5C6-05FB81DFFC03}" name="Rate" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{6E3636B9-97B1-4231-848A-84020E8CD1A3}" name="Final Billing Amount" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="75">
       <calculatedColumnFormula>IFERROR(Table27[[#This Row],[Actual Hours]]*Table27[[#This Row],[Rate]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D4793879-E2F3-472D-8E9B-2105426B8F6B}" name="1" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{E486E4A8-41C0-4AFF-BB9A-B45102FE633C}" name="2" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{4A4F0742-3816-4B9E-9F0A-7F96C051FEC1}" name="3" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{24E6AAA5-D211-40AD-808B-294BCA6071A0}" name="4" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{70086128-55FD-4B5D-AE29-F9B280C62589}" name="5" totalsRowFunction="sum" dataDxfId="77" totalsRowDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{F86580CD-5B8C-4123-A821-D46F4A6EC4F6}" name="6" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{6F961A6F-63D3-4D42-AE89-E86613A2C14F}" name="7" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="27"/>
-    <tableColumn id="13" xr3:uid="{554D2725-AA19-4B75-A7B9-2A8387E18BDC}" name="8" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="26"/>
-    <tableColumn id="14" xr3:uid="{63D8B858-12A3-4A0B-A826-BE3186D9F21F}" name="9" totalsRowFunction="sum" dataDxfId="73" totalsRowDxfId="25"/>
-    <tableColumn id="15" xr3:uid="{B19FFC3C-59E3-475E-8113-0CE80BFE9635}" name="10" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="24"/>
-    <tableColumn id="16" xr3:uid="{D5D68AE4-2278-40D7-BFED-A0B492731248}" name="11" totalsRowFunction="sum" dataDxfId="71" totalsRowDxfId="23"/>
-    <tableColumn id="17" xr3:uid="{30651372-2451-4B32-ACB6-665FBA20F98B}" name="12" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="22"/>
-    <tableColumn id="18" xr3:uid="{D0FAAF2E-7D84-4E6B-90D7-80E1E12AFF8B}" name="13" totalsRowFunction="sum" dataDxfId="69" totalsRowDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{DA2E8EE3-9D9F-4FCB-B634-0F5CDF5A99C6}" name="14" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{27F58B70-B194-47CB-B393-AB8FB149C0CD}" name="15" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{A626272B-9B6C-49DD-B884-912D4983CB24}" name="16" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{2D327AA4-6E26-4B2B-A188-C61BB78F1A4F}" name="17" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="17"/>
-    <tableColumn id="23" xr3:uid="{81418BDA-3722-4FD6-A1AC-D19EC0365795}" name="18" totalsRowLabel="0" dataDxfId="64" totalsRowDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{748261B7-3B42-48B0-B56D-6066930E4F45}" name="19" totalsRowLabel="0" dataDxfId="63" totalsRowDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{27D1FC17-EEA9-4BBA-9BF0-F488BB07BC27}" name="20" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="14"/>
-    <tableColumn id="26" xr3:uid="{CE5F7E04-EA29-476A-8C04-10311E5AA245}" name="21" totalsRowFunction="sum" dataDxfId="61" totalsRowDxfId="13"/>
-    <tableColumn id="27" xr3:uid="{6A1ED293-6B3A-4F5F-878E-BC6852209689}" name="22" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="12"/>
-    <tableColumn id="28" xr3:uid="{DED4194D-2CE9-4CED-A0E1-5517221173CE}" name="23" totalsRowFunction="sum" dataDxfId="59" totalsRowDxfId="11"/>
-    <tableColumn id="29" xr3:uid="{8F702A72-079F-4DDC-8889-42FF1892A8D9}" name="24" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="10"/>
-    <tableColumn id="30" xr3:uid="{952EC144-0583-4A0E-9606-7D1C67415A11}" name="25" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="9"/>
-    <tableColumn id="31" xr3:uid="{02E5AB35-203D-45F7-968D-89FFFD7605BD}" name="26" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="8"/>
-    <tableColumn id="32" xr3:uid="{74C12FEA-BDE5-479D-93E6-E783309D1823}" name="27" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="7"/>
-    <tableColumn id="33" xr3:uid="{9340BC5C-0231-47F4-BAAB-F3EC43CAB876}" name="28" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="6"/>
-    <tableColumn id="34" xr3:uid="{3EAF38D2-F687-4B74-91B5-FCEBE8F0AF14}" name="29" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="5"/>
-    <tableColumn id="35" xr3:uid="{EA5A44B8-FFE4-4939-963A-C719186ADF9D}" name="30" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{F4FC74EA-7D3E-4BCD-81C3-3AD31C403124}" name="31" dataDxfId="51" totalsRowDxfId="3"/>
-    <tableColumn id="38" xr3:uid="{04D5C202-3AEB-4435-9159-2F359239778C}" name="Status" dataDxfId="50" totalsRowDxfId="2">
+    <tableColumn id="6" xr3:uid="{D4793879-E2F3-472D-8E9B-2105426B8F6B}" name="1" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{E486E4A8-41C0-4AFF-BB9A-B45102FE633C}" name="2" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{4A4F0742-3816-4B9E-9F0A-7F96C051FEC1}" name="3" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{24E6AAA5-D211-40AD-808B-294BCA6071A0}" name="4" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{70086128-55FD-4B5D-AE29-F9B280C62589}" name="5" totalsRowFunction="sum" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="11" xr3:uid="{F86580CD-5B8C-4123-A821-D46F4A6EC4F6}" name="6" totalsRowFunction="sum" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{6F961A6F-63D3-4D42-AE89-E86613A2C14F}" name="7" totalsRowFunction="sum" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="13" xr3:uid="{554D2725-AA19-4B75-A7B9-2A8387E18BDC}" name="8" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{63D8B858-12A3-4A0B-A826-BE3186D9F21F}" name="9" totalsRowFunction="sum" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{B19FFC3C-59E3-475E-8113-0CE80BFE9635}" name="10" totalsRowFunction="sum" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{D5D68AE4-2278-40D7-BFED-A0B492731248}" name="11" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{30651372-2451-4B32-ACB6-665FBA20F98B}" name="12" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="18" xr3:uid="{D0FAAF2E-7D84-4E6B-90D7-80E1E12AFF8B}" name="13" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="19" xr3:uid="{DA2E8EE3-9D9F-4FCB-B634-0F5CDF5A99C6}" name="14" totalsRowFunction="sum" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="20" xr3:uid="{27F58B70-B194-47CB-B393-AB8FB149C0CD}" name="15" totalsRowFunction="sum" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="21" xr3:uid="{A626272B-9B6C-49DD-B884-912D4983CB24}" name="16" totalsRowFunction="sum" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{2D327AA4-6E26-4B2B-A188-C61BB78F1A4F}" name="17" totalsRowFunction="sum" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="23" xr3:uid="{81418BDA-3722-4FD6-A1AC-D19EC0365795}" name="18" totalsRowLabel="0" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{748261B7-3B42-48B0-B56D-6066930E4F45}" name="19" totalsRowLabel="0" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="25" xr3:uid="{27D1FC17-EEA9-4BBA-9BF0-F488BB07BC27}" name="20" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{CE5F7E04-EA29-476A-8C04-10311E5AA245}" name="21" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="27" xr3:uid="{6A1ED293-6B3A-4F5F-878E-BC6852209689}" name="22" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="28" xr3:uid="{DED4194D-2CE9-4CED-A0E1-5517221173CE}" name="23" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="29" xr3:uid="{8F702A72-079F-4DDC-8889-42FF1892A8D9}" name="24" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="30" xr3:uid="{952EC144-0583-4A0E-9606-7D1C67415A11}" name="25" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="31" xr3:uid="{02E5AB35-203D-45F7-968D-89FFFD7605BD}" name="26" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="32" xr3:uid="{74C12FEA-BDE5-479D-93E6-E783309D1823}" name="27" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="33" xr3:uid="{9340BC5C-0231-47F4-BAAB-F3EC43CAB876}" name="28" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="34" xr3:uid="{3EAF38D2-F687-4B74-91B5-FCEBE8F0AF14}" name="29" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="35" xr3:uid="{EA5A44B8-FFE4-4939-963A-C719186ADF9D}" name="30" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="36" xr3:uid="{F4FC74EA-7D3E-4BCD-81C3-3AD31C403124}" name="31" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="38" xr3:uid="{04D5C202-3AEB-4435-9159-2F359239778C}" name="Status" dataDxfId="12" totalsRowDxfId="11">
       <calculatedColumnFormula>_xlfn.IFNA(_xlfn.XLOOKUP(Table27[[#This Row],[Name]],Table1[Name],Table1[Status]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{CF7A8946-2CDE-4C23-8580-6C1FEFBCBE31}" name="Billing %" totalsRowFunction="custom" dataDxfId="49" totalsRowDxfId="1">
+    <tableColumn id="37" xr3:uid="{CF7A8946-2CDE-4C23-8580-6C1FEFBCBE31}" name="Billing %" totalsRowFunction="custom" dataDxfId="10" totalsRowDxfId="9">
       <calculatedColumnFormula>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</calculatedColumnFormula>
       <totalsRowFormula>Table27[[#Totals],[Actual Hours]]/Table27[[#Totals],[Max Billable Hours]]</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{564CFFE4-041D-EA42-91CE-7E2B074AFE9C}" name="Cost" dataDxfId="41" totalsRowDxfId="0"/>
+    <tableColumn id="41" xr3:uid="{564CFFE4-041D-EA42-91CE-7E2B074AFE9C}" name="Cost" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -2468,7 +2468,7 @@
     <tableColumn id="7" xr3:uid="{B318C1B5-DDBA-40C0-AEBF-DD0C8A713529}" name="Emp ID"/>
     <tableColumn id="1" xr3:uid="{61F66100-680B-43D4-9643-C6580DB98E19}" name="Name"/>
     <tableColumn id="2" xr3:uid="{1F30959A-FED7-4B38-99D5-577C9DC6ADAE}" name="Role as per SoW"/>
-    <tableColumn id="3" xr3:uid="{A55B2A4F-0240-4914-A04B-C9F5FB352057}" name="Onboard date" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{A55B2A4F-0240-4914-A04B-C9F5FB352057}" name="Onboard date" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{339185EB-1D1C-416C-A786-1371EE5CAED8}" name="Status"/>
     <tableColumn id="5" xr3:uid="{FD8EC05C-4379-49DC-8B99-679FAC8FE7DF}" name="LWD"/>
     <tableColumn id="6" xr3:uid="{A16E1008-E82E-4B63-9D13-91E4A58BEC57}" name="Billable Hours per day"/>
@@ -3020,10 +3020,10 @@
       </c>
     </row>
     <row r="5" spans="2:45" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="32"/>
+      <c r="C5" s="27"/>
       <c r="E5" s="6" t="s">
         <v>70</v>
       </c>
@@ -3149,11 +3149,11 @@
       </c>
     </row>
     <row r="6" spans="2:45" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="33">
+      <c r="B6" s="28">
         <f>SUM(Table27[Final Billing Amount])</f>
         <v>80264</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="29"/>
       <c r="E6" s="20" t="s">
         <v>87</v>
       </c>
@@ -3279,15 +3279,15 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS6" s="38">
+      <c r="AS6" s="26">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="30"/>
       <c r="E7" s="20" t="s">
         <v>88</v>
       </c>
@@ -3413,7 +3413,7 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS7" s="38">
+      <c r="AS7" s="26">
         <v>20</v>
       </c>
     </row>
@@ -3545,16 +3545,16 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS8" s="38">
+      <c r="AS8" s="26">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B9" s="36">
+      <c r="B9" s="31">
         <f>SUM(Table27[Max Billable Hours])</f>
         <v>2524</v>
       </c>
-      <c r="C9" s="36"/>
+      <c r="C9" s="31"/>
       <c r="E9" s="20" t="s">
         <v>90</v>
       </c>
@@ -3680,13 +3680,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>3.8181818181818183</v>
       </c>
-      <c r="AS9" s="38">
+      <c r="AS9" s="26">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
       <c r="E10" s="20" t="s">
         <v>91</v>
       </c>
@@ -3812,13 +3812,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS10" s="38">
+      <c r="AS10" s="26">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
       <c r="E11" s="20" t="s">
         <v>92</v>
       </c>
@@ -3944,13 +3944,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS11" s="38">
+      <c r="AS11" s="26">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
       <c r="E12" s="20" t="s">
         <v>93</v>
       </c>
@@ -4076,13 +4076,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS12" s="38">
+      <c r="AS12" s="26">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
       <c r="E13" s="20" t="s">
         <v>94</v>
       </c>
@@ -4208,13 +4208,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS13" s="38">
+      <c r="AS13" s="26">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
       <c r="E14" s="20" t="s">
         <v>95</v>
       </c>
@@ -4340,13 +4340,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS14" s="38">
+      <c r="AS14" s="26">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
       <c r="E15" s="20" t="s">
         <v>96</v>
       </c>
@@ -4472,13 +4472,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS15" s="38">
+      <c r="AS15" s="26">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
       <c r="E16" s="20" t="s">
         <v>97</v>
       </c>
@@ -4604,13 +4604,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS16" s="38">
+      <c r="AS16" s="26">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
       <c r="E17" s="20" t="s">
         <v>98</v>
       </c>
@@ -4736,13 +4736,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS17" s="38">
+      <c r="AS17" s="26">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
       <c r="E18" s="20" t="s">
         <v>99</v>
       </c>
@@ -4868,13 +4868,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS18" s="38">
+      <c r="AS18" s="26">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
       <c r="E19" s="20" t="s">
         <v>100</v>
       </c>
@@ -5000,13 +5000,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS19" s="38">
+      <c r="AS19" s="26">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
       <c r="E20" s="20" t="s">
         <v>101</v>
       </c>
@@ -5132,13 +5132,13 @@
         <f>Table27[[#This Row],[Actual Hours]]/Table27[[#This Row],[Max Billable Hours]]</f>
         <v>1</v>
       </c>
-      <c r="AS20" s="38">
+      <c r="AS20" s="26">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
@@ -5284,78 +5284,78 @@
       <c r="AS21" s="10"/>
     </row>
     <row r="23" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="37"/>
+      <c r="C23" s="32"/>
     </row>
     <row r="24" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B24" s="31">
+      <c r="B24" s="38">
         <f>SUM(Table27[Actual Hours])</f>
         <v>2648</v>
       </c>
-      <c r="C24" s="31"/>
+      <c r="C24" s="38"/>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
     </row>
     <row r="27" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="26"/>
+      <c r="C27" s="33"/>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B28" s="27">
+      <c r="B28" s="34">
         <f>SUM(Table27[Actual Hours])/SUM(Table27[Max Billable Hours])</f>
         <v>1.0491283676703644</v>
       </c>
-      <c r="C28" s="27"/>
+      <c r="C28" s="34"/>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
     </row>
     <row r="31" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
     </row>
     <row r="32" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B24:C25"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B9:C21"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B24:C25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J4:AP4">
-    <cfRule type="beginsWith" dxfId="47" priority="23" operator="beginsWith" text="S">
+    <cfRule type="beginsWith" dxfId="5" priority="23" operator="beginsWith" text="S">
       <formula>LEFT(J4,LEN("S"))="S"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:AQ21">
-    <cfRule type="beginsWith" dxfId="46" priority="20" operator="beginsWith" text="H">
+    <cfRule type="beginsWith" dxfId="4" priority="20" operator="beginsWith" text="H">
       <formula>LEFT(L6,LEN("H"))="H"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="OF">
+    <cfRule type="containsText" dxfId="3" priority="21" operator="containsText" text="OF">
       <formula>NOT(ISERROR(SEARCH("OF",L6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="22" operator="containsText" text="WO">
+    <cfRule type="containsText" dxfId="2" priority="22" operator="containsText" text="WO">
       <formula>NOT(ISERROR(SEARCH("WO",L6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5863,12 +5863,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D13:D14">
-    <cfRule type="expression" dxfId="43" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>LEFT(#REF!,1)="S"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEFT(#REF!,1)="S"</formula>
     </cfRule>
   </conditionalFormatting>
